--- a/04_Figures/F05/c_data/F05_supplementary.xlsx
+++ b/04_Figures/F05/c_data/F05_supplementary.xlsx
@@ -37034,10 +37034,10 @@
         <v>355</v>
       </c>
       <c r="D2" t="n">
-        <v>-3.9371007585132</v>
+        <v>-3.93710075851277</v>
       </c>
       <c r="E2" t="n">
-        <v>3.58874043431259</v>
+        <v>3.58874043431221</v>
       </c>
       <c r="F2" t="n">
         <v>-0.597411491529304</v>
@@ -37046,10 +37046,10 @@
         <v>0.471959805145943</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00671080196697798</v>
+        <v>0.006710801966989</v>
       </c>
       <c r="I2" t="n">
-        <v>3.58874043431259</v>
+        <v>3.58874043431221</v>
       </c>
     </row>
     <row r="3">
@@ -37063,10 +37063,10 @@
         <v>355</v>
       </c>
       <c r="D3" t="n">
-        <v>-4.04859953116317</v>
+        <v>-4.04859953116007</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4307237061489</v>
+        <v>3.43072370614627</v>
       </c>
       <c r="F3" t="n">
         <v>-2.27189871419792</v>
@@ -37075,10 +37075,10 @@
         <v>1.71883830144357</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00000000267703007540086</v>
+        <v>0.00000000267703007547216</v>
       </c>
       <c r="I3" t="n">
-        <v>3.4307237061489</v>
+        <v>3.43072370614627</v>
       </c>
     </row>
     <row r="4">
@@ -37092,22 +37092,22 @@
         <v>353</v>
       </c>
       <c r="D4" t="n">
-        <v>4.15570306232582</v>
+        <v>4.15570306232449</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.27770767069571</v>
+        <v>-3.27770767069465</v>
       </c>
       <c r="F4" t="n">
-        <v>0.777014506338922</v>
+        <v>0.777014506338926</v>
       </c>
       <c r="G4" t="n">
         <v>-0.522010739619176</v>
       </c>
       <c r="H4" t="n">
-        <v>0.000795973306634181</v>
+        <v>0.000795973306637826</v>
       </c>
       <c r="I4" t="n">
-        <v>3.27770767069571</v>
+        <v>3.27770767069465</v>
       </c>
     </row>
     <row r="5">
@@ -37121,22 +37121,22 @@
         <v>355</v>
       </c>
       <c r="D5" t="n">
-        <v>-3.69288733286679</v>
+        <v>-3.69288733286625</v>
       </c>
       <c r="E5" t="n">
-        <v>2.90305005690763</v>
+        <v>2.90305005690723</v>
       </c>
       <c r="F5" t="n">
         <v>-0.565429589561255</v>
       </c>
       <c r="G5" t="n">
-        <v>0.384221208705149</v>
+        <v>0.384221208705153</v>
       </c>
       <c r="H5" t="n">
-        <v>0.013134434957003</v>
+        <v>0.0131344349570227</v>
       </c>
       <c r="I5" t="n">
-        <v>2.90305005690763</v>
+        <v>2.90305005690723</v>
       </c>
     </row>
     <row r="6">
@@ -37150,22 +37150,22 @@
         <v>353</v>
       </c>
       <c r="D6" t="n">
-        <v>3.26703253728556</v>
+        <v>3.26703253728417</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.82722820233256</v>
+        <v>-2.82722820233133</v>
       </c>
       <c r="F6" t="n">
-        <v>0.715061284822703</v>
+        <v>0.715061284822706</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5348906483379</v>
+        <v>-0.534890648337896</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0107810327048408</v>
+        <v>0.0107810327048776</v>
       </c>
       <c r="I6" t="n">
-        <v>2.82722820233256</v>
+        <v>2.82722820233133</v>
       </c>
     </row>
     <row r="7">
@@ -37179,22 +37179,22 @@
         <v>353</v>
       </c>
       <c r="D7" t="n">
-        <v>2.65901742676927</v>
+        <v>2.65901742676655</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.82372456460538</v>
+        <v>-2.82372456460248</v>
       </c>
       <c r="F7" t="n">
         <v>1.67716055476474</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.592076886423479</v>
+        <v>-0.592076886423476</v>
       </c>
       <c r="H7" t="n">
-        <v>0.000706663582811587</v>
+        <v>0.000706663582820863</v>
       </c>
       <c r="I7" t="n">
-        <v>2.82372456460538</v>
+        <v>2.82372456460248</v>
       </c>
     </row>
     <row r="8">
@@ -37208,22 +37208,22 @@
         <v>355</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.35852882481332</v>
+        <v>-4.35852882481273</v>
       </c>
       <c r="E8" t="n">
-        <v>2.80929708939559</v>
+        <v>2.80929708939522</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.662057570983201</v>
+        <v>-0.662057570983205</v>
       </c>
       <c r="G8" t="n">
-        <v>0.374929812381282</v>
+        <v>0.374929812381286</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00145898227448936</v>
+        <v>0.00145898227449291</v>
       </c>
       <c r="I8" t="n">
-        <v>2.80929708939559</v>
+        <v>2.80929708939522</v>
       </c>
     </row>
     <row r="9">
@@ -37237,22 +37237,22 @@
         <v>353</v>
       </c>
       <c r="D9" t="n">
-        <v>3.90839238914544</v>
+        <v>3.90839238914686</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.7707894464288</v>
+        <v>-2.77078944642966</v>
       </c>
       <c r="F9" t="n">
         <v>0.433731740226015</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.265790192708053</v>
+        <v>-0.265790192708039</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0266944179173494</v>
+        <v>0.0266944179173084</v>
       </c>
       <c r="I9" t="n">
-        <v>2.7707894464288</v>
+        <v>2.77078944642966</v>
       </c>
     </row>
     <row r="10">
@@ -37266,22 +37266,22 @@
         <v>355</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5259140162855</v>
+        <v>-3.52591401628621</v>
       </c>
       <c r="E10" t="n">
-        <v>2.5842654267832</v>
+        <v>2.58426542678376</v>
       </c>
       <c r="F10" t="n">
         <v>-0.423499479740652</v>
       </c>
       <c r="G10" t="n">
-        <v>0.268307379019333</v>
+        <v>0.268307379019337</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0487971661454301</v>
+        <v>0.0487971661454003</v>
       </c>
       <c r="I10" t="n">
-        <v>2.5842654267832</v>
+        <v>2.58426542678376</v>
       </c>
     </row>
     <row r="11">
@@ -37295,22 +37295,22 @@
         <v>355</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.31074482037404</v>
+        <v>-4.3107448203813</v>
       </c>
       <c r="E11" t="n">
-        <v>2.57847100644854</v>
+        <v>2.57847100645296</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.31896550820726</v>
+        <v>-0.318965508207256</v>
       </c>
       <c r="G11" t="n">
-        <v>0.16491797569994</v>
+        <v>0.164917975699943</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0448317333503638</v>
+        <v>0.0448317333500267</v>
       </c>
       <c r="I11" t="n">
-        <v>2.57847100644854</v>
+        <v>2.57847100645296</v>
       </c>
     </row>
     <row r="12">
@@ -37324,22 +37324,22 @@
         <v>355</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.74668058079195</v>
+        <v>-3.74668058079064</v>
       </c>
       <c r="E12" t="n">
-        <v>2.57566249509019</v>
+        <v>2.57566249508927</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.850908212601206</v>
+        <v>-0.85090821260121</v>
       </c>
       <c r="G12" t="n">
-        <v>0.445165103086296</v>
+        <v>0.445165103086294</v>
       </c>
       <c r="H12" t="n">
-        <v>0.00203041058238492</v>
+        <v>0.00203041058239604</v>
       </c>
       <c r="I12" t="n">
-        <v>2.57566249509019</v>
+        <v>2.57566249508927</v>
       </c>
     </row>
     <row r="13">
@@ -37353,22 +37353,22 @@
         <v>353</v>
       </c>
       <c r="D13" t="n">
-        <v>5.55146503524437</v>
+        <v>5.55146503524348</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.56897353270499</v>
+        <v>-2.56897353270459</v>
       </c>
       <c r="F13" t="n">
-        <v>0.882946331508698</v>
+        <v>0.882946331508695</v>
       </c>
       <c r="G13" t="n">
         <v>-0.34205561187164</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0000035764514688769</v>
+        <v>0.00000357645146889897</v>
       </c>
       <c r="I13" t="n">
-        <v>2.56897353270499</v>
+        <v>2.56897353270459</v>
       </c>
     </row>
     <row r="14">
@@ -37382,22 +37382,22 @@
         <v>353</v>
       </c>
       <c r="D14" t="n">
-        <v>4.67581743017993</v>
+        <v>4.67581743018008</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.48852679370839</v>
+        <v>-2.48852679370841</v>
       </c>
       <c r="F14" t="n">
         <v>0.624535587336357</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.287313677843002</v>
+        <v>-0.287313677842995</v>
       </c>
       <c r="H14" t="n">
-        <v>0.001021648713579</v>
+        <v>0.00102164871357993</v>
       </c>
       <c r="I14" t="n">
-        <v>2.48852679370839</v>
+        <v>2.48852679370841</v>
       </c>
     </row>
     <row r="15">
@@ -37411,22 +37411,22 @@
         <v>355</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.70413441558413</v>
+        <v>-3.70413441558189</v>
       </c>
       <c r="E15" t="n">
-        <v>2.44815673279938</v>
+        <v>2.44815673279791</v>
       </c>
       <c r="F15" t="n">
         <v>-1.35117187669119</v>
       </c>
       <c r="G15" t="n">
-        <v>0.771929099725785</v>
+        <v>0.771929099725789</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0000303679570412233</v>
+        <v>0.0000303679570415596</v>
       </c>
       <c r="I15" t="n">
-        <v>2.44815673279938</v>
+        <v>2.44815673279791</v>
       </c>
     </row>
     <row r="16">
@@ -37440,22 +37440,22 @@
         <v>353</v>
       </c>
       <c r="D16" t="n">
-        <v>5.02446440630786</v>
+        <v>5.02446440631811</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.39862875136079</v>
+        <v>-2.39862875136557</v>
       </c>
       <c r="F16" t="n">
         <v>0.347919302860035</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.143570800232045</v>
+        <v>-0.143570800232037</v>
       </c>
       <c r="H16" t="n">
-        <v>0.013853981468482</v>
+        <v>0.0138539814683113</v>
       </c>
       <c r="I16" t="n">
-        <v>2.39862875136079</v>
+        <v>2.39862875136557</v>
       </c>
     </row>
     <row r="17">
@@ -37469,22 +37469,22 @@
         <v>353</v>
       </c>
       <c r="D17" t="n">
-        <v>4.22753783558619</v>
+        <v>4.22753783558398</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.32543062510177</v>
+        <v>-2.32543062510052</v>
       </c>
       <c r="F17" t="n">
         <v>1.08135071850107</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.415925667311125</v>
+        <v>-0.415925667311118</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0000544233334221523</v>
+        <v>0.0000544233334227095</v>
       </c>
       <c r="I17" t="n">
-        <v>2.32543062510177</v>
+        <v>2.32543062510052</v>
       </c>
     </row>
     <row r="18">
@@ -37498,10 +37498,10 @@
         <v>355</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.49215147165076</v>
+        <v>-3.49215147164909</v>
       </c>
       <c r="E18" t="n">
-        <v>2.29037622689093</v>
+        <v>2.29037622688984</v>
       </c>
       <c r="F18" t="n">
         <v>-1.1116745118082</v>
@@ -37510,10 +37510,10 @@
         <v>0.62672221369505</v>
       </c>
       <c r="H18" t="n">
-        <v>0.000929610416181754</v>
+        <v>0.00092961041618995</v>
       </c>
       <c r="I18" t="n">
-        <v>2.29037622689093</v>
+        <v>2.29037622688984</v>
       </c>
     </row>
     <row r="19">
@@ -37527,22 +37527,22 @@
         <v>353</v>
       </c>
       <c r="D19" t="n">
-        <v>4.66361096669426</v>
+        <v>4.66361096669469</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.26397517522534</v>
+        <v>-2.26397517522548</v>
       </c>
       <c r="F19" t="n">
         <v>0.60023717740048</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.251875875038547</v>
+        <v>-0.251875875038539</v>
       </c>
       <c r="H19" t="n">
-        <v>0.00137122108003963</v>
+        <v>0.00137122108004</v>
       </c>
       <c r="I19" t="n">
-        <v>2.26397517522534</v>
+        <v>2.26397517522548</v>
       </c>
     </row>
     <row r="20">
@@ -37556,10 +37556,10 @@
         <v>353</v>
       </c>
       <c r="D20" t="n">
-        <v>2.68372044151471</v>
+        <v>2.68372044151303</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.22491111535392</v>
+        <v>-2.22491111535253</v>
       </c>
       <c r="F20" t="n">
         <v>1.01123088006005</v>
@@ -37568,10 +37568,10 @@
         <v>-0.456230554894423</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0123508247795362</v>
+        <v>0.0123508247796063</v>
       </c>
       <c r="I20" t="n">
-        <v>2.22491111535392</v>
+        <v>2.22491111535253</v>
       </c>
     </row>
     <row r="21">
@@ -37585,22 +37585,22 @@
         <v>353</v>
       </c>
       <c r="D21" t="n">
-        <v>4.26031066716109</v>
+        <v>4.26031066716238</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.07434614117303</v>
+        <v>-2.07434614117363</v>
       </c>
       <c r="F21" t="n">
         <v>0.489040005966505</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.205599986846916</v>
+        <v>-0.205599986846913</v>
       </c>
       <c r="H21" t="n">
-        <v>0.00948691987057074</v>
+        <v>0.00948691987055741</v>
       </c>
       <c r="I21" t="n">
-        <v>2.07434614117303</v>
+        <v>2.07434614117363</v>
       </c>
     </row>
     <row r="22">
@@ -37614,10 +37614,10 @@
         <v>353</v>
       </c>
       <c r="D22" t="n">
-        <v>4.0395925984408</v>
+        <v>4.03959259843835</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.00088539344208</v>
+        <v>-2.00088539344086</v>
       </c>
       <c r="F22" t="n">
         <v>1.12441874217729</v>
@@ -37626,10 +37626,10 @@
         <v>-0.425439908729789</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0000631431400318923</v>
+        <v>0.0000631431400325751</v>
       </c>
       <c r="I22" t="n">
-        <v>2.00088539344208</v>
+        <v>2.00088539344086</v>
       </c>
     </row>
     <row r="23">
@@ -37643,22 +37643,22 @@
         <v>355</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.9447419114759</v>
+        <v>-5.94474191147884</v>
       </c>
       <c r="E23" t="n">
-        <v>1.97061743133106</v>
+        <v>1.97061743133207</v>
       </c>
       <c r="F23" t="n">
         <v>-0.621798340911273</v>
       </c>
       <c r="G23" t="n">
-        <v>0.178169437902948</v>
+        <v>0.178169437902952</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0000541723788258809</v>
+        <v>0.0000541723788256336</v>
       </c>
       <c r="I23" t="n">
-        <v>1.97061743133106</v>
+        <v>1.97061743133207</v>
       </c>
     </row>
     <row r="24">
@@ -37672,22 +37672,22 @@
         <v>355</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.78371545876976</v>
+        <v>-2.78371545876934</v>
       </c>
       <c r="E24" t="n">
-        <v>1.95550506308851</v>
+        <v>1.95550506308819</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.651423926186304</v>
+        <v>-0.651423926186311</v>
       </c>
       <c r="G24" t="n">
         <v>0.286696817312706</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0455003640129484</v>
+        <v>0.045500364013011</v>
       </c>
       <c r="I24" t="n">
-        <v>1.95550506308851</v>
+        <v>1.95550506308819</v>
       </c>
     </row>
     <row r="25">
@@ -37701,22 +37701,22 @@
         <v>353</v>
       </c>
       <c r="D25" t="n">
-        <v>3.84486120200567</v>
+        <v>3.84486120200834</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.94827948130359</v>
+        <v>-1.9482794813049</v>
       </c>
       <c r="F25" t="n">
         <v>0.372299321422634</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.163071163661403</v>
+        <v>-0.1630711636614</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0479865278570393</v>
+        <v>0.0479865278569015</v>
       </c>
       <c r="I25" t="n">
-        <v>1.94827948130359</v>
+        <v>1.9482794813049</v>
       </c>
     </row>
     <row r="26">
@@ -37730,22 +37730,22 @@
         <v>355</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.78331763690464</v>
+        <v>-3.78331763690407</v>
       </c>
       <c r="E26" t="n">
-        <v>1.90844777926481</v>
+        <v>1.90844777926455</v>
       </c>
       <c r="F26" t="n">
         <v>-0.582372536006311</v>
       </c>
       <c r="G26" t="n">
-        <v>0.25393507796478</v>
+        <v>0.253935077964783</v>
       </c>
       <c r="H26" t="n">
-        <v>0.00972539177638922</v>
+        <v>0.0097253917764055</v>
       </c>
       <c r="I26" t="n">
-        <v>1.90844777926481</v>
+        <v>1.90844777926455</v>
       </c>
     </row>
   </sheetData>

--- a/04_Figures/F05/c_data/F05_supplementary.xlsx
+++ b/04_Figures/F05/c_data/F05_supplementary.xlsx
@@ -28240,22 +28240,22 @@
         <v>312</v>
       </c>
       <c r="D2" t="n">
-        <v>-3.9371007585131</v>
+        <v>-3.937100758513</v>
       </c>
       <c r="E2" t="n">
-        <v>3.58874043431251</v>
+        <v>3.5887404343125</v>
       </c>
       <c r="F2" t="n">
         <v>-0.597411491529307</v>
       </c>
       <c r="G2" t="n">
-        <v>0.471959805145946</v>
+        <v>0.471959805145957</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00671080196698083</v>
+        <v>0.00671080196698345</v>
       </c>
       <c r="I2" t="n">
-        <v>3.58874043431251</v>
+        <v>3.5887404343125</v>
       </c>
     </row>
     <row r="3">
@@ -28269,22 +28269,22 @@
         <v>312</v>
       </c>
       <c r="D3" t="n">
-        <v>-4.04859953116219</v>
+        <v>-4.04859953116145</v>
       </c>
       <c r="E3" t="n">
-        <v>3.43072370614807</v>
+        <v>3.43072370614742</v>
       </c>
       <c r="F3" t="n">
         <v>-2.27189871419792</v>
       </c>
       <c r="G3" t="n">
-        <v>1.71883830144357</v>
+        <v>1.71883830144356</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00000000267703007542339</v>
+        <v>0.00000000267703007544035</v>
       </c>
       <c r="I3" t="n">
-        <v>3.43072370614807</v>
+        <v>3.43072370614742</v>
       </c>
     </row>
     <row r="4">
@@ -28298,22 +28298,22 @@
         <v>310</v>
       </c>
       <c r="D4" t="n">
-        <v>4.15570306232539</v>
+        <v>4.15570306232507</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.27770767069535</v>
+        <v>-3.27770767069489</v>
       </c>
       <c r="F4" t="n">
         <v>0.777014506338922</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.522010739619173</v>
+        <v>-0.522010739619141</v>
       </c>
       <c r="H4" t="n">
-        <v>0.000795973306635362</v>
+        <v>0.000795973306636249</v>
       </c>
       <c r="I4" t="n">
-        <v>3.27770767069535</v>
+        <v>3.27770767069489</v>
       </c>
     </row>
     <row r="5">
@@ -28327,22 +28327,22 @@
         <v>312</v>
       </c>
       <c r="D5" t="n">
-        <v>-3.69288733286661</v>
+        <v>-3.69288733286662</v>
       </c>
       <c r="E5" t="n">
-        <v>2.90305005690751</v>
+        <v>2.90305005690752</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.565429589561255</v>
+        <v>-0.565429589561276</v>
       </c>
       <c r="G5" t="n">
-        <v>0.384221208705153</v>
+        <v>0.384221208705167</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0131344349570094</v>
+        <v>0.0131344349570088</v>
       </c>
       <c r="I5" t="n">
-        <v>2.90305005690751</v>
+        <v>2.90305005690752</v>
       </c>
     </row>
     <row r="6">
@@ -28356,22 +28356,22 @@
         <v>310</v>
       </c>
       <c r="D6" t="n">
-        <v>3.26703253728514</v>
+        <v>3.26703253728484</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.82722820233214</v>
+        <v>-2.82722820233191</v>
       </c>
       <c r="F6" t="n">
-        <v>0.715061284822706</v>
+        <v>0.715061284822713</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.534890648337893</v>
+        <v>-0.534890648337903</v>
       </c>
       <c r="H6" t="n">
-        <v>0.010781032704852</v>
+        <v>0.0107810327048595</v>
       </c>
       <c r="I6" t="n">
-        <v>2.82722820233214</v>
+        <v>2.82722820233191</v>
       </c>
     </row>
     <row r="7">
@@ -28385,22 +28385,22 @@
         <v>310</v>
       </c>
       <c r="D7" t="n">
-        <v>2.6590174267684</v>
+        <v>2.65901742676775</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.82372456460444</v>
+        <v>-2.82372456460376</v>
       </c>
       <c r="F7" t="n">
         <v>1.67716055476474</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.592076886423476</v>
+        <v>-0.592076886423477</v>
       </c>
       <c r="H7" t="n">
-        <v>0.000706663582814541</v>
+        <v>0.000706663582816761</v>
       </c>
       <c r="I7" t="n">
-        <v>2.82372456460444</v>
+        <v>2.82372456460376</v>
       </c>
     </row>
     <row r="8">
@@ -28414,22 +28414,22 @@
         <v>312</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.35852882481319</v>
+        <v>-4.35852882481296</v>
       </c>
       <c r="E8" t="n">
-        <v>2.80929708939554</v>
+        <v>2.80929708939542</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.662057570983212</v>
+        <v>-0.662057570983198</v>
       </c>
       <c r="G8" t="n">
-        <v>0.374929812381293</v>
+        <v>0.374929812381289</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00145898227449016</v>
+        <v>0.00145898227449151</v>
       </c>
       <c r="I8" t="n">
-        <v>2.80929708939554</v>
+        <v>2.80929708939542</v>
       </c>
     </row>
     <row r="9">
@@ -28443,22 +28443,22 @@
         <v>310</v>
       </c>
       <c r="D9" t="n">
-        <v>3.90839238914596</v>
+        <v>3.90839238914623</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.77078944642898</v>
+        <v>-2.7707894464291</v>
       </c>
       <c r="F9" t="n">
-        <v>0.433731740226023</v>
+        <v>0.433731740226015</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.265790192708039</v>
+        <v>-0.265790192708028</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0266944179173322</v>
+        <v>0.0266944179173265</v>
       </c>
       <c r="I9" t="n">
-        <v>2.77078944642898</v>
+        <v>2.7707894464291</v>
       </c>
     </row>
     <row r="10">
@@ -28472,22 +28472,22 @@
         <v>312</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.52591401628575</v>
+        <v>-3.52591401628598</v>
       </c>
       <c r="E10" t="n">
-        <v>2.5842654267834</v>
+        <v>2.58426542678359</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.423499479740656</v>
+        <v>-0.423499479740663</v>
       </c>
       <c r="G10" t="n">
-        <v>0.268307379019337</v>
+        <v>0.268307379019344</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0487971661454176</v>
+        <v>0.0487971661454044</v>
       </c>
       <c r="I10" t="n">
-        <v>2.5842654267834</v>
+        <v>2.58426542678359</v>
       </c>
     </row>
     <row r="11">
@@ -28501,22 +28501,22 @@
         <v>312</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.31074482037632</v>
+        <v>-4.3107448203782</v>
       </c>
       <c r="E11" t="n">
-        <v>2.57847100645004</v>
+        <v>2.57847100645141</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.318965508207256</v>
+        <v>-0.318965508207267</v>
       </c>
       <c r="G11" t="n">
-        <v>0.164917975699947</v>
+        <v>0.164917975699968</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0448317333502588</v>
+        <v>0.0448317333501664</v>
       </c>
       <c r="I11" t="n">
-        <v>2.57847100645004</v>
+        <v>2.57847100645141</v>
       </c>
     </row>
     <row r="12">
@@ -28530,22 +28530,22 @@
         <v>312</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.74668058079154</v>
+        <v>-3.74668058079128</v>
       </c>
       <c r="E12" t="n">
-        <v>2.57566249508989</v>
+        <v>2.57566249508978</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.85090821260121</v>
+        <v>-0.850908212601222</v>
       </c>
       <c r="G12" t="n">
-        <v>0.445165103086294</v>
+        <v>0.445165103086312</v>
       </c>
       <c r="H12" t="n">
-        <v>0.00203041058238838</v>
+        <v>0.00203041058239062</v>
       </c>
       <c r="I12" t="n">
-        <v>2.57566249508989</v>
+        <v>2.57566249508978</v>
       </c>
     </row>
     <row r="13">
@@ -28559,22 +28559,22 @@
         <v>310</v>
       </c>
       <c r="D13" t="n">
-        <v>5.55146503524407</v>
+        <v>5.55146503524391</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.56897353270486</v>
+        <v>-2.56897353270478</v>
       </c>
       <c r="F13" t="n">
-        <v>0.882946331508695</v>
+        <v>0.882946331508698</v>
       </c>
       <c r="G13" t="n">
         <v>-0.34205561187164</v>
       </c>
       <c r="H13" t="n">
-        <v>0.00000357645146888429</v>
+        <v>0.00000357645146888861</v>
       </c>
       <c r="I13" t="n">
-        <v>2.56897353270486</v>
+        <v>2.56897353270478</v>
       </c>
     </row>
     <row r="14">
@@ -28588,22 +28588,22 @@
         <v>310</v>
       </c>
       <c r="D14" t="n">
-        <v>4.67581743018004</v>
+        <v>4.67581743018006</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.48852679370842</v>
+        <v>-2.48852679370831</v>
       </c>
       <c r="F14" t="n">
         <v>0.624535587336364</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.287313677843002</v>
+        <v>-0.287313677842988</v>
       </c>
       <c r="H14" t="n">
-        <v>0.00102164871357909</v>
+        <v>0.00102164871357933</v>
       </c>
       <c r="I14" t="n">
-        <v>2.48852679370842</v>
+        <v>2.48852679370831</v>
       </c>
     </row>
     <row r="15">
@@ -28617,22 +28617,22 @@
         <v>312</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.70413441558342</v>
+        <v>-3.70413441558288</v>
       </c>
       <c r="E15" t="n">
-        <v>2.44815673279892</v>
+        <v>2.44815673279858</v>
       </c>
       <c r="F15" t="n">
         <v>-1.35117187669119</v>
       </c>
       <c r="G15" t="n">
-        <v>0.771929099725789</v>
+        <v>0.771929099725792</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0000303679570413302</v>
+        <v>0.0000303679570414112</v>
       </c>
       <c r="I15" t="n">
-        <v>2.44815673279892</v>
+        <v>2.44815673279858</v>
       </c>
     </row>
     <row r="16">
@@ -28646,22 +28646,22 @@
         <v>310</v>
       </c>
       <c r="D16" t="n">
-        <v>5.02446440631114</v>
+        <v>5.0244644063136</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.39862875136224</v>
+        <v>-2.39862875136335</v>
       </c>
       <c r="F16" t="n">
         <v>0.347919302860035</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.143570800232037</v>
+        <v>-0.143570800232034</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0138539814684273</v>
+        <v>0.0138539814683864</v>
       </c>
       <c r="I16" t="n">
-        <v>2.39862875136224</v>
+        <v>2.39862875136335</v>
       </c>
     </row>
     <row r="17">
@@ -28675,22 +28675,22 @@
         <v>310</v>
       </c>
       <c r="D17" t="n">
-        <v>4.22753783558549</v>
+        <v>4.22753783558491</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.32543062510134</v>
+        <v>-2.32543062510099</v>
       </c>
       <c r="F17" t="n">
-        <v>1.08135071850107</v>
+        <v>1.08135071850106</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.415925667311118</v>
+        <v>-0.415925667311107</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0000544233334223296</v>
+        <v>0.0000544233334224764</v>
       </c>
       <c r="I17" t="n">
-        <v>2.32543062510134</v>
+        <v>2.32543062510099</v>
       </c>
     </row>
     <row r="18">
@@ -28704,22 +28704,22 @@
         <v>312</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.49215147165021</v>
+        <v>-3.49215147164983</v>
       </c>
       <c r="E18" t="n">
-        <v>2.29037622689058</v>
+        <v>2.29037622689036</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1116745118082</v>
+        <v>-1.11167451180821</v>
       </c>
       <c r="G18" t="n">
-        <v>0.62672221369505</v>
+        <v>0.626722213695061</v>
       </c>
       <c r="H18" t="n">
-        <v>0.00092961041618443</v>
+        <v>0.000929610416186294</v>
       </c>
       <c r="I18" t="n">
-        <v>2.29037622689058</v>
+        <v>2.29037622689036</v>
       </c>
     </row>
     <row r="19">
@@ -28733,22 +28733,22 @@
         <v>310</v>
       </c>
       <c r="D19" t="n">
-        <v>4.66361096669447</v>
+        <v>4.6636109666946</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.26397517522541</v>
+        <v>-2.26397517522534</v>
       </c>
       <c r="F19" t="n">
-        <v>0.600237177400487</v>
+        <v>0.600237177400491</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.251875875038547</v>
+        <v>-0.251875875038532</v>
       </c>
       <c r="H19" t="n">
-        <v>0.00137122108003944</v>
+        <v>0.00137122108003938</v>
       </c>
       <c r="I19" t="n">
-        <v>2.26397517522541</v>
+        <v>2.26397517522534</v>
       </c>
     </row>
     <row r="20">
@@ -28762,22 +28762,22 @@
         <v>310</v>
       </c>
       <c r="D20" t="n">
-        <v>2.68372044151418</v>
+        <v>2.68372044151374</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.22491111535348</v>
+        <v>-2.22491111535308</v>
       </c>
       <c r="F20" t="n">
-        <v>1.01123088006005</v>
+        <v>1.01123088006004</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.456230554894423</v>
+        <v>-0.456230554894409</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0123508247795584</v>
+        <v>0.0123508247795768</v>
       </c>
       <c r="I20" t="n">
-        <v>2.22491111535348</v>
+        <v>2.22491111535308</v>
       </c>
     </row>
     <row r="21">
@@ -28791,22 +28791,22 @@
         <v>310</v>
       </c>
       <c r="D21" t="n">
-        <v>4.26031066716153</v>
+        <v>4.26031066716193</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0743461411732</v>
+        <v>-2.07434614117353</v>
       </c>
       <c r="F21" t="n">
-        <v>0.489040005966508</v>
+        <v>0.489040005966519</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.205599986846913</v>
+        <v>-0.205599986846931</v>
       </c>
       <c r="H21" t="n">
-        <v>0.00948691987056568</v>
+        <v>0.00948691987056013</v>
       </c>
       <c r="I21" t="n">
-        <v>2.0743461411732</v>
+        <v>2.07434614117353</v>
       </c>
     </row>
     <row r="22">
@@ -28820,22 +28820,22 @@
         <v>310</v>
       </c>
       <c r="D22" t="n">
-        <v>4.03959259844001</v>
+        <v>4.0395925984395</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.00088539344167</v>
+        <v>-2.00088539344139</v>
       </c>
       <c r="F22" t="n">
-        <v>1.12441874217729</v>
+        <v>1.12441874217732</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.425439908729786</v>
+        <v>-0.425439908729789</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0000631431400321122</v>
+        <v>0.0000631431400322445</v>
       </c>
       <c r="I22" t="n">
-        <v>2.00088539344167</v>
+        <v>2.00088539344139</v>
       </c>
     </row>
     <row r="23">
@@ -28849,22 +28849,22 @@
         <v>312</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.9447419114768</v>
+        <v>-5.9447419114775</v>
       </c>
       <c r="E23" t="n">
-        <v>1.97061743133141</v>
+        <v>1.97061743133176</v>
       </c>
       <c r="F23" t="n">
         <v>-0.621798340911269</v>
       </c>
       <c r="G23" t="n">
-        <v>0.178169437902952</v>
+        <v>0.178169437902962</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0000541723788258092</v>
+        <v>0.0000541723788257518</v>
       </c>
       <c r="I23" t="n">
-        <v>1.97061743133141</v>
+        <v>1.97061743133176</v>
       </c>
     </row>
     <row r="24">
@@ -28878,22 +28878,22 @@
         <v>312</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.78371545876965</v>
+        <v>-2.78371545876957</v>
       </c>
       <c r="E24" t="n">
-        <v>1.95550506308841</v>
+        <v>1.95550506308838</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.651423926186311</v>
+        <v>-0.651423926186318</v>
       </c>
       <c r="G24" t="n">
-        <v>0.286696817312706</v>
+        <v>0.286696817312713</v>
       </c>
       <c r="H24" t="n">
-        <v>0.045500364012966</v>
+        <v>0.0455003640129779</v>
       </c>
       <c r="I24" t="n">
-        <v>1.95550506308841</v>
+        <v>1.95550506308838</v>
       </c>
     </row>
     <row r="25">
@@ -28907,22 +28907,22 @@
         <v>310</v>
       </c>
       <c r="D25" t="n">
-        <v>3.84486120200649</v>
+        <v>3.84486120200712</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.94827948130398</v>
+        <v>-1.94827948130413</v>
       </c>
       <c r="F25" t="n">
         <v>0.372299321422631</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.1630711636614</v>
+        <v>-0.163071163661385</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0479865278569991</v>
+        <v>0.0479865278569666</v>
       </c>
       <c r="I25" t="n">
-        <v>1.94827948130398</v>
+        <v>1.94827948130413</v>
       </c>
     </row>
     <row r="26">
@@ -28936,22 +28936,22 @@
         <v>312</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.78331763690444</v>
+        <v>-3.78331763690435</v>
       </c>
       <c r="E26" t="n">
-        <v>1.90844777926477</v>
+        <v>1.90844777926481</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.582372536006307</v>
+        <v>-0.582372536006314</v>
       </c>
       <c r="G26" t="n">
-        <v>0.253935077964787</v>
+        <v>0.253935077964801</v>
       </c>
       <c r="H26" t="n">
-        <v>0.00972539177639508</v>
+        <v>0.00972539177639759</v>
       </c>
       <c r="I26" t="n">
-        <v>1.90844777926477</v>
+        <v>1.90844777926481</v>
       </c>
     </row>
   </sheetData>
